--- a/diseases/d050/2020-2025.xlsx
+++ b/diseases/d050/2020-2025.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1653,9 +1650,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2393,9 +2387,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -3133,9 +3124,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4021,9 +4009,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -4761,9 +4746,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5501,9 +5483,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6389,9 +6368,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -7129,9 +7105,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7869,9 +7842,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8757,9 +8727,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -9497,9 +9464,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10385,9 +10349,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -11125,9 +11086,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -11865,9 +11823,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12605,9 +12560,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -13493,9 +13445,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -14233,9 +14182,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -14973,9 +14919,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -15861,9 +15804,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -16601,9 +16541,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17489,9 +17426,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -18229,9 +18163,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -18969,9 +18900,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -19857,9 +19785,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -20597,9 +20522,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -21337,9 +21259,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -22225,9 +22144,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -22965,9 +22881,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -23705,9 +23618,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -24593,9 +24503,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -25333,9 +25240,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -26073,9 +25977,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -26961,9 +26862,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -27701,9 +27599,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -28441,9 +28336,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -29329,9 +29221,6 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0</v>
       </c>
@@ -30069,9 +29958,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -30809,9 +30695,6 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
@@ -31845,9 +31728,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -32585,9 +32465,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -33325,9 +33202,6 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
@@ -34213,9 +34087,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -34953,9 +34824,6 @@
       <c r="O233" t="n">
         <v>0</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0</v>
       </c>
@@ -35841,9 +35709,6 @@
       <c r="O239" t="n">
         <v>0</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
@@ -36581,9 +36446,6 @@
       <c r="O244" t="n">
         <v>0</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0</v>
       </c>
@@ -37321,9 +37183,6 @@
       <c r="O249" t="n">
         <v>0</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0</v>
       </c>
@@ -38209,9 +38068,6 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -38949,9 +38805,6 @@
       <c r="O260" t="n">
         <v>0</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0</v>
       </c>
@@ -39689,9 +39542,6 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -40577,9 +40427,6 @@
       <c r="O271" t="n">
         <v>0</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0</v>
       </c>
@@ -41317,9 +41164,6 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0</v>
       </c>
@@ -42057,9 +41901,6 @@
       <c r="O281" t="n">
         <v>0</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0</v>
       </c>
@@ -42945,9 +42786,6 @@
       <c r="O287" t="n">
         <v>0</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0</v>
       </c>
@@ -43685,9 +43523,6 @@
       <c r="O292" t="n">
         <v>0</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0</v>
       </c>
@@ -44425,9 +44260,6 @@
       <c r="O297" t="n">
         <v>0</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0</v>
       </c>
@@ -45313,9 +45145,6 @@
       <c r="O303" t="n">
         <v>0</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0</v>
       </c>
@@ -46053,9 +45882,6 @@
       <c r="O308" t="n">
         <v>0</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0</v>
       </c>
@@ -46941,9 +46767,6 @@
       <c r="O314" t="n">
         <v>0</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0</v>
       </c>
@@ -47681,9 +47504,6 @@
       <c r="O319" t="n">
         <v>0</v>
       </c>
-      <c r="Q319" t="n">
-        <v>0</v>
-      </c>
       <c r="R319" t="n">
         <v>0</v>
       </c>
@@ -48421,9 +48241,6 @@
       <c r="O324" t="n">
         <v>0</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0</v>
       </c>
@@ -49309,9 +49126,6 @@
       <c r="O330" t="n">
         <v>0</v>
       </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
       <c r="R330" t="n">
         <v>0</v>
       </c>
@@ -50049,9 +49863,6 @@
       <c r="O335" t="n">
         <v>0</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0</v>
       </c>
@@ -50789,9 +50600,6 @@
       <c r="O340" t="n">
         <v>0</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0</v>
       </c>
@@ -51529,9 +51337,6 @@
       <c r="O345" t="n">
         <v>0</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0</v>
       </c>
@@ -52417,9 +52222,6 @@
       <c r="O351" t="n">
         <v>0</v>
       </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
       <c r="R351" t="n">
         <v>0</v>
       </c>
@@ -53157,9 +52959,6 @@
       <c r="O356" t="n">
         <v>0</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>0</v>
       </c>
@@ -54045,9 +53844,6 @@
       <c r="O362" t="n">
         <v>0</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0</v>
       </c>
@@ -54785,9 +54581,6 @@
       <c r="O367" t="n">
         <v>0</v>
       </c>
-      <c r="Q367" t="n">
-        <v>0</v>
-      </c>
       <c r="R367" t="n">
         <v>0</v>
       </c>
@@ -55525,9 +55318,6 @@
       <c r="O372" t="n">
         <v>0</v>
       </c>
-      <c r="Q372" t="n">
-        <v>0</v>
-      </c>
       <c r="R372" t="n">
         <v>0</v>
       </c>
@@ -56413,9 +56203,6 @@
       <c r="O378" t="n">
         <v>0</v>
       </c>
-      <c r="Q378" t="n">
-        <v>0</v>
-      </c>
       <c r="R378" t="n">
         <v>0</v>
       </c>
@@ -57151,9 +56938,6 @@
         <v>0</v>
       </c>
       <c r="O383" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q383" t="n">
         <v>0</v>
       </c>
       <c r="R383" t="n">
